--- a/samples/ss_slcg_ingest.xlsx
+++ b/samples/ss_slcg_ingest.xlsx
@@ -495,7 +495,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R16"/>
+  <dimension ref="A1:U16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -536,57 +536,72 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Bus 150 kV</t>
+          <t>Bus HV</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
+          <t>Bus LV</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t>Jumlah Trafo</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Jumlah Kapasitor</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Catatan Simbol</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Jumlah Sirkit Bay</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Status Operasi</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Role</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Status Kerawanan</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>No Kerawanan</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Wilayah</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Sudut Pandang</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>Latitude</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>Longitude</t>
         </is>
       </c>
     </row>
@@ -623,24 +638,25 @@
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr">
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr">
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr">
         <is>
           <t>Banten</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -675,24 +691,25 @@
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr">
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr">
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr">
         <is>
           <t>Banten</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -727,24 +744,25 @@
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr">
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr">
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr">
         <is>
           <t>Banten</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -779,24 +797,25 @@
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr">
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr">
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr">
         <is>
           <t>Banten</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -830,37 +849,38 @@
           <t>2</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
         <is>
           <t>SRLYA</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr">
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
         <is>
           <t>Rawan</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>Banten</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -894,37 +914,38 @@
           <t>1</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
         <is>
           <t>SRLYA</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr">
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
         <is>
           <t>Rawan</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="R7" t="inlineStr">
         <is>
           <t>Banten</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -958,37 +979,38 @@
           <t>4</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
         <is>
           <t>CLBRU</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr">
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
         <is>
           <t>Rawan</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="R8" t="inlineStr">
         <is>
           <t>Banten</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1023,28 +1045,29 @@
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr">
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
         <is>
           <t>Rawan</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="Q9" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
+      <c r="R9" t="inlineStr">
         <is>
           <t>Banten</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1079,28 +1102,29 @@
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr">
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
         <is>
           <t>Rawan</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="Q10" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr">
+      <c r="R10" t="inlineStr">
         <is>
           <t>Banten</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1135,24 +1159,25 @@
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr">
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr"/>
-      <c r="Q11" t="inlineStr">
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr">
         <is>
           <t>Banten</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1187,24 +1212,25 @@
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr">
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr"/>
-      <c r="Q12" t="inlineStr">
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr">
         <is>
           <t>Banten</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1239,28 +1265,29 @@
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr">
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
         <is>
           <t>Rawan</t>
         </is>
       </c>
-      <c r="P13" t="inlineStr">
+      <c r="Q13" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="Q13" t="inlineStr">
+      <c r="R13" t="inlineStr">
         <is>
           <t>Banten</t>
         </is>
       </c>
-      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1295,28 +1322,29 @@
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr">
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
         <is>
           <t>Rawan</t>
         </is>
       </c>
-      <c r="P14" t="inlineStr">
+      <c r="Q14" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="Q14" t="inlineStr">
+      <c r="R14" t="inlineStr">
         <is>
           <t>Banten</t>
         </is>
       </c>
-      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1351,28 +1379,29 @@
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
-      <c r="O15" t="inlineStr">
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
         <is>
           <t>Rawan</t>
         </is>
       </c>
-      <c r="P15" t="inlineStr">
+      <c r="Q15" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="Q15" t="inlineStr">
+      <c r="R15" t="inlineStr">
         <is>
           <t>Banten</t>
         </is>
       </c>
-      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1407,28 +1436,29 @@
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
-      <c r="O16" t="inlineStr">
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
         <is>
           <t>Rawan</t>
         </is>
       </c>
-      <c r="P16" t="inlineStr">
+      <c r="Q16" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="Q16" t="inlineStr">
+      <c r="R16" t="inlineStr">
         <is>
           <t>Banten</t>
         </is>
       </c>
-      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/samples/ss_slcg_ingest.xlsx
+++ b/samples/ss_slcg_ingest.xlsx
@@ -2178,7 +2178,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:J11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2204,25 +2204,30 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>Jenis</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>Tegangan</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Jumlah Sirkit</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Status Operasi</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>No Kerawanan</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Sudut Pandang</t>
         </is>
@@ -2247,21 +2252,22 @@
           <t>SLRDA</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr">
         <is>
           <t>150 kV</t>
         </is>
       </c>
-      <c r="F2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
+      <c r="G2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -2282,21 +2288,22 @@
           <t>SLRDA</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr">
         <is>
           <t>150 kV</t>
         </is>
       </c>
-      <c r="F3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
+      <c r="G3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -2317,21 +2324,22 @@
           <t>PENDO</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr">
         <is>
           <t>150 kV</t>
         </is>
       </c>
-      <c r="F4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
+      <c r="G4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -2352,21 +2360,22 @@
           <t>PENI</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr">
         <is>
           <t>150 kV</t>
         </is>
       </c>
-      <c r="F5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr"/>
+      <c r="G5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -2387,21 +2396,22 @@
           <t>PENI</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr">
         <is>
           <t>150 kV</t>
         </is>
       </c>
-      <c r="F6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr"/>
+      <c r="G6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -2422,21 +2432,22 @@
           <t>MCCI5</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr">
         <is>
           <t>150 kV</t>
         </is>
       </c>
-      <c r="F7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr"/>
+      <c r="G7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -2457,21 +2468,22 @@
           <t>CLBRU</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr">
         <is>
           <t>150 kV</t>
         </is>
       </c>
-      <c r="F8" t="n">
-        <v>1</v>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr"/>
+      <c r="G8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -2492,21 +2504,22 @@
           <t>CLBRU</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr">
         <is>
           <t>150 kV</t>
         </is>
       </c>
-      <c r="F9" t="n">
-        <v>1</v>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr"/>
+      <c r="G9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -2527,21 +2540,22 @@
           <t>CLGON</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr">
         <is>
           <t>150 kV</t>
         </is>
       </c>
-      <c r="F10" t="n">
-        <v>1</v>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr"/>
+      <c r="G10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -2562,21 +2576,22 @@
           <t>MTSUI</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr">
         <is>
           <t>150 kV</t>
         </is>
       </c>
-      <c r="F11" t="n">
-        <v>1</v>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr"/>
+      <c r="G11" t="n">
+        <v>1</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
